--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -945,22 +945,22 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1048,7 +1048,1339 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -776,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -887,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +934,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -937,7 +945,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -965,32 +973,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -998,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1034,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1175,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1259,7 +1275,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1270,7 +1286,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1397,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1458,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1508,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1569,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1592,7 +1608,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1603,7 +1619,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1680,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1730,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1791,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1841,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1902,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1952,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2013,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2063,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2124,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2174,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2235,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2285,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2277,22 +2293,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>07:57</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2325,12 +2341,12 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2344,7 +2360,7 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2369,7 +2385,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2380,7 +2396,903 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1092,32 +1092,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1125,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1149,33 +1153,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1425,32 +1433,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1458,7 +1470,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1482,33 +1494,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1680,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1719,7 +1735,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1758,32 +1774,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:53</t>
@@ -1791,7 +1811,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1815,33 +1835,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1941,7 +1965,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2013,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2052,7 +2076,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2124,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2202,32 +2226,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2235,7 +2263,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2259,33 +2287,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2313,32 +2345,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -2346,7 +2382,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2370,33 +2406,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2497,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2511,7 +2551,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2612,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2683,7 +2723,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2722,7 +2762,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2794,7 +2834,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2848,7 +2888,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2906,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2909,7 +2949,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2923,7 +2963,7 @@
       <c r="T22" s="2" t="inlineStr"/>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -3020,7 +3060,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3059,7 +3099,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3131,7 +3171,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3189,22 +3229,22 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3237,12 +3277,12 @@
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3256,41 +3296,1171 @@
       <c r="T25" s="2" t="inlineStr"/>
       <c r="U25" s="2" t="inlineStr">
         <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W25" s="2" t="inlineStr">
+      <c r="W27" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X25" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y25" s="2" t="inlineStr">
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z25" s="2" t="inlineStr">
+      <c r="Z27" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
+      <c r="AA27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr"/>
-      <c r="AC25" s="2" t="inlineStr">
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1624,18 +1624,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1700,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1811,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1850,7 +1854,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1865,7 +1869,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1930,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1965,18 +1969,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2263,7 +2271,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2317,7 +2325,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2390,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2436,7 +2444,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2464,32 +2472,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2497,7 +2509,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2521,17 +2533,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2541,17 +2553,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2579,32 +2591,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:53</t>
@@ -2612,7 +2628,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2636,17 +2652,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2656,13 +2672,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2743,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,7 +2854,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2873,7 +2893,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2888,7 +2908,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3080,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3171,7 +3191,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3210,7 +3230,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3282,7 +3302,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3336,7 +3356,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3417,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3436,7 +3456,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3451,7 +3471,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3479,32 +3499,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3512,7 +3536,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3536,33 +3560,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3651,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3701,32 +3729,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:53</t>
@@ -3734,7 +3766,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3758,33 +3790,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3881,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3899,7 +3935,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3996,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3999,7 +4035,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4014,7 +4050,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4111,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4186,7 +4222,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4297,7 +4333,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4351,7 +4387,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4359,22 +4395,22 @@
       <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4407,12 +4443,12 @@
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4466,6 +4502,692 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC41"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>99.5</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,18 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,18 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1049,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1470,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1524,7 +1532,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1639,7 +1647,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1815,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1859,17 +1867,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1938,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1984,7 +1992,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2053,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2084,18 +2092,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2283,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2310,7 +2322,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2325,7 +2337,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2402,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2434,17 +2446,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2521,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2548,14 +2560,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>99.5</t>
@@ -2563,7 +2575,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2694,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2755,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2782,18 +2794,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2870,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2893,22 +2909,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3096,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3119,18 +3135,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3211,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3356,7 +3376,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3437,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3471,7 +3491,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3556,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3590,7 +3610,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3671,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,7 +3786,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3820,7 +3840,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3901,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3920,7 +3940,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3935,7 +3955,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3963,32 +3983,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:53</t>
@@ -3996,7 +4020,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4020,17 +4044,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4040,17 +4064,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4078,32 +4102,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4111,7 +4139,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4135,33 +4163,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4189,32 +4221,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4222,7 +4258,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4246,33 +4282,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4300,32 +4340,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4333,7 +4377,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4357,17 +4401,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4377,17 +4421,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4492,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4526,32 +4570,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4559,7 +4607,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4583,33 +4631,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB36" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4637,32 +4689,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4670,7 +4726,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4694,37 +4750,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4841,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4839,7 +4895,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4956,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4954,7 +5010,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5071,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5069,7 +5125,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5186,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5174,17 +5230,707 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr">
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
         <is>
           <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,17 +943,13 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1068,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1187,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1517,22 +1513,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1819,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1862,17 +1858,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1938,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1977,17 +1973,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2053,7 +2049,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2092,7 +2088,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2107,7 +2103,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2279,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2322,22 +2318,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2398,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2451,12 +2447,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2517,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2755,7 +2751,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2809,7 +2805,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2866,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2924,7 +2920,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3092,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3140,17 +3136,13 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3368,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3429,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3476,22 +3468,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3778,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3825,17 +3817,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3901,7 +3893,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3940,22 +3932,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4012,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4059,17 +4051,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4139,7 +4131,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4178,7 +4170,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4193,7 +4185,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4250,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4312,7 +4304,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4350,24 +4342,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4377,7 +4369,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4426,12 +4418,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4570,36 +4562,32 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4607,7 +4595,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4631,17 +4619,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4651,17 +4639,13 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4710,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4780,7 +4764,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4923,32 +4907,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4956,7 +4944,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4980,37 +4968,37 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5038,32 +5026,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:53</t>
@@ -5071,7 +5063,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5095,32 +5087,32 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5153,32 +5145,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:53</t>
@@ -5186,7 +5182,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5210,32 +5206,32 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5268,32 +5264,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5325,37 +5325,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5805,17 +5805,13 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5872,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5930,6 +5926,581 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
           <t>3/18</t>
         </is>
       </c>

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,18 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,12 +1057,12 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1068,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1513,7 +1517,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1528,7 +1532,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1647,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1743,7 +1747,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1819,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1868,12 +1872,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1938,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2049,7 +2053,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2093,17 +2097,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2283,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2328,12 +2332,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2456,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2521,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2556,22 +2560,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2694,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2755,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2790,22 +2794,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2870,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2905,12 +2909,12 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -2920,7 +2924,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3096,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3131,18 +3135,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3376,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3437,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3468,7 +3476,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3483,7 +3491,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3610,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3671,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3702,7 +3710,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3778,7 +3786,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,7 +3901,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3942,12 +3950,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4020,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4061,12 +4069,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4139,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4175,17 +4183,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4258,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4289,22 +4297,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4431,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4603,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4634,18 +4642,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB36" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4722,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4749,12 +4761,12 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4764,7 +4776,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4891,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4956,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4983,7 +4995,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -4998,7 +5010,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5075,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5155,24 +5167,24 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5182,7 +5194,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5231,12 +5243,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5274,24 +5286,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5301,7 +5313,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5350,12 +5362,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5383,32 +5395,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -5416,7 +5432,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5440,17 +5456,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5460,17 +5476,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5498,32 +5514,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5531,7 +5551,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5555,37 +5575,37 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5613,32 +5633,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5646,7 +5670,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5670,37 +5694,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5728,32 +5752,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5761,7 +5789,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5785,33 +5813,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5839,32 +5871,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5872,7 +5908,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5896,27 +5932,27 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -5926,7 +5962,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5987,7 +6023,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6026,7 +6062,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6041,7 +6077,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6085,7 @@
       <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -6097,12 +6133,12 @@
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6141,22 +6177,18 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB49" s="2" t="inlineStr">
-        <is>
-          <t>84.5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr"/>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -6164,22 +6196,22 @@
       <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6217,7 +6249,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6231,7 +6263,7 @@
       <c r="T50" s="2" t="inlineStr"/>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
@@ -6261,17 +6293,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6279,22 +6311,22 @@
       <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6327,12 +6359,12 @@
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6346,7 +6378,7 @@
       <c r="T51" s="2" t="inlineStr"/>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
@@ -6376,17 +6408,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6394,22 +6426,22 @@
       <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6442,12 +6474,12 @@
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6461,47 +6493,737 @@
       <c r="T52" s="2" t="inlineStr"/>
       <c r="U52" s="2" t="inlineStr">
         <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
           <t>13:30</t>
         </is>
       </c>
-      <c r="V52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W52" s="2" t="inlineStr">
+      <c r="W53" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X52" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y52" s="2" t="inlineStr">
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z52" s="2" t="inlineStr">
+      <c r="Z53" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>95.3</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB52" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>3/18</t>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1522,17 +1522,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1747,18 +1747,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1827,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1862,7 +1866,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1877,7 +1881,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1992,7 +1996,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2057,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2107,7 +2111,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2287,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2337,7 +2341,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2460,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2525,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2570,12 +2574,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2698,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2759,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2809,7 +2813,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2874,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2919,12 +2923,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3100,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3145,12 +3149,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3380,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3441,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3481,17 +3485,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3614,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3675,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3710,18 +3714,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3848,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3909,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3955,7 +3963,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4028,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4059,7 +4067,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4074,7 +4082,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4139,7 +4147,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4193,7 +4201,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4266,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4312,7 +4320,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4439,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4611,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4652,12 +4660,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4730,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4771,12 +4779,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4899,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4964,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5000,17 +5008,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5137,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5202,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5233,7 +5241,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5248,7 +5256,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5321,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5367,7 +5375,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5440,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5486,7 +5494,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5559,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5605,7 +5613,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5643,24 +5651,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5670,7 +5678,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5719,12 +5727,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5762,12 +5770,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -5789,7 +5797,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5838,12 +5846,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5881,24 +5889,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5908,7 +5916,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5957,12 +5965,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5990,32 +5998,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6023,7 +6035,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6047,17 +6059,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6067,17 +6079,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6105,32 +6117,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6138,7 +6154,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6162,33 +6178,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB49" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6323,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6384,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6403,7 +6423,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6418,7 +6438,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6499,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6533,7 +6553,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6614,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6648,7 +6668,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6729,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6763,7 +6783,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6844,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6873,12 +6893,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6939,7 +6959,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6988,12 +7008,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7074,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7103,12 +7123,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7116,22 +7136,22 @@
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7169,7 +7189,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7208,22 +7228,363 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>10/18</t>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2096,22 +2096,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2326,22 +2326,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2803,17 +2803,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3948,22 +3948,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4186,22 +4186,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5360,22 +5360,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5479,22 +5479,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6351,32 +6351,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:53</t>
@@ -6384,7 +6388,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6408,17 +6412,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6428,12 +6432,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6466,32 +6470,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6499,7 +6507,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6523,37 +6531,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6581,32 +6589,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6614,7 +6626,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6638,37 +6650,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6696,32 +6708,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6729,7 +6745,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6753,17 +6769,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6773,17 +6789,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6860,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6959,7 +6975,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7074,7 +7090,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7128,7 +7144,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7189,7 +7205,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7300,7 +7316,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7354,7 +7370,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7431,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7530,7 +7546,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7574,17 +7590,473 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>12/18</t>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,17 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2445,14 +2445,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>87.0</t>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2683,14 +2683,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>90.0</t>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2798,22 +2798,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2913,22 +2913,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3144,17 +3144,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4305,22 +4305,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4424,14 +4424,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>87.0</t>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq25推进至seq33，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4508,10 +4508,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>五莲路凌河路</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="S35" s="2" t="inlineStr"/>
-      <c r="T35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq19映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4539,7 +4551,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4611,7 +4623,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4655,17 +4667,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4742,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4769,22 +4781,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4812,12 +4824,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq25推进至seq29，推进4站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4845,7 +4857,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4853,10 +4865,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>五莲路凌河路</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq19映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -4884,7 +4908,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4899,7 +4923,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4988,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5018,7 +5042,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5226,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5251,7 +5275,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5321,7 +5345,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5440,7 +5464,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5489,7 +5513,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5559,7 +5583,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5598,22 +5622,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5702,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5722,12 +5746,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5797,7 +5821,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5841,17 +5865,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5940,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5955,22 +5979,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6059,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6089,7 +6113,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6178,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6208,7 +6232,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6361,24 +6385,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6388,7 +6412,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6437,7 +6461,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6507,7 +6531,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6599,12 +6623,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -6626,7 +6650,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6675,7 +6699,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6708,36 +6732,32 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6745,7 +6765,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6769,37 +6789,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6827,32 +6847,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6860,7 +6884,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6884,17 +6908,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6904,12 +6928,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -6942,32 +6966,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6975,7 +7003,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6999,17 +7027,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7019,17 +7047,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7057,32 +7085,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7090,7 +7122,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7114,37 +7146,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7205,7 +7237,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7316,7 +7348,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7370,7 +7402,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7431,7 +7463,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7485,7 +7517,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7578,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7595,7 +7627,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7661,7 +7693,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7772,7 +7804,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7887,7 +7919,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7949,22 +7981,22 @@
       <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -7997,12 +8029,12 @@
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8016,47 +8048,733 @@
       <c r="T65" s="2" t="inlineStr"/>
       <c r="U65" s="2" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
           <t>15:25</t>
         </is>
       </c>
-      <c r="V65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W65" s="2" t="inlineStr">
+      <c r="W66" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X65" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y65" s="2" t="inlineStr">
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z65" s="2" t="inlineStr">
+      <c r="Z66" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
+      <c r="AA66" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr">
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
         <is>
           <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1402,18 +1402,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1517,17 +1521,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1593,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1647,7 +1651,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1752,17 +1756,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1866,14 +1870,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>91.2</t>
@@ -1881,7 +1885,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2061,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2101,17 +2105,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2176,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2211,18 +2215,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2326,17 +2334,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2406,7 +2414,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2460,7 +2468,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2587,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2652,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2688,12 +2696,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2759,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2813,7 +2821,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2882,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2928,7 +2936,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3108,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3139,7 +3147,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3215,7 +3223,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3334,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3370,17 +3378,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3449,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3480,17 +3488,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3560,7 +3568,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3614,7 +3622,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3683,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3719,17 +3727,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3917,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3948,17 +3956,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4028,7 +4036,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4067,14 +4075,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>91.2</t>
@@ -4082,7 +4090,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4155,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4191,17 +4199,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4274,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4320,7 +4328,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4393,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4439,7 +4447,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4508,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,7 +4631,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4662,7 +4670,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4742,7 +4750,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4796,7 +4804,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4837,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq25推进至seq29，推进4站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq25推进至seq38，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4857,7 +4865,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4923,7 +4931,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4988,7 +4996,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5027,17 +5035,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5226,7 +5234,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5265,14 +5273,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>91.2</t>
@@ -5280,7 +5288,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5353,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5384,17 +5392,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5464,7 +5472,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5508,17 +5516,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5591,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5637,7 +5645,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5764,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5829,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5860,7 +5868,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5940,7 +5948,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5994,7 +6002,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6067,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6098,17 +6106,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6178,7 +6186,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6222,17 +6230,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6420,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6451,14 +6459,14 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>91.2</t>
@@ -6466,7 +6474,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6539,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6570,17 +6578,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6650,7 +6658,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6694,17 +6702,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6773,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6819,7 +6827,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6938,7 +6946,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7011,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7042,7 +7050,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7122,7 +7130,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7176,7 +7184,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7204,32 +7212,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7237,7 +7249,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7261,33 +7273,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7315,32 +7331,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7348,7 +7368,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7372,32 +7392,32 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7430,32 +7450,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7463,7 +7487,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7487,17 +7511,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7507,17 +7531,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7545,32 +7569,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:53</t>
@@ -7578,7 +7606,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7602,29 +7630,29 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>91.2</t>
@@ -7632,7 +7660,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7660,32 +7688,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7693,7 +7725,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7717,33 +7749,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7771,32 +7807,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7804,7 +7844,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7828,32 +7868,32 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7886,32 +7926,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -7919,7 +7963,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7943,17 +7987,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -7963,17 +8007,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8001,32 +8045,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:53</t>
@@ -8034,7 +8082,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8058,17 +8106,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8078,12 +8126,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8116,32 +8164,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8149,7 +8201,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8173,17 +8225,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8193,17 +8245,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8316,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8375,7 +8427,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8429,7 +8481,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8542,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8544,7 +8596,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8552,22 +8604,22 @@
       <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8600,12 +8652,12 @@
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8644,22 +8696,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8667,22 +8719,22 @@
       <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8715,12 +8767,12 @@
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8734,7 +8786,7 @@
       <c r="T71" s="2" t="inlineStr"/>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
@@ -8759,22 +8811,712 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>10/18</t>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>91.2</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC77"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,18 +1291,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1417,7 +1421,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1597,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1636,7 +1640,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1651,7 +1655,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2061,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2100,7 +2104,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2110,7 +2114,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2176,7 +2180,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2295,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2414,7 +2418,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2453,22 +2457,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2691,22 +2695,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2806,7 +2810,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2821,7 +2825,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2921,22 +2925,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3112,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3223,7 +3227,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3262,18 +3266,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3342,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3373,7 +3381,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3388,7 +3396,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3457,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3568,7 +3576,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3607,7 +3615,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3622,7 +3630,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3925,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,7 +4044,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,7 +4163,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4194,7 +4202,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4204,7 +4212,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4274,7 +4282,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4313,7 +4321,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4328,7 +4336,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4401,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4432,22 +4440,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4516,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4559,18 +4567,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,7 +4762,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4789,22 +4801,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4877,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4916,7 +4928,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4931,7 +4943,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4996,7 +5008,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5234,7 +5246,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5353,7 +5365,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5472,7 +5484,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5511,7 +5523,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5521,7 +5533,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5591,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5630,7 +5642,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5645,7 +5657,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5948,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5987,22 +5999,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6067,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6420,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6539,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6658,7 +6670,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6697,7 +6709,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6707,7 +6719,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6773,7 +6785,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6812,7 +6824,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6827,7 +6839,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7023,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7130,7 +7142,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7169,22 +7181,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7261,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7303,7 +7315,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7380,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7606,7 +7618,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,7 +7737,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7844,7 +7856,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7963,7 +7975,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8002,7 +8014,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8017,7 +8029,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8055,12 +8067,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
@@ -8082,7 +8094,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8121,22 +8133,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8174,24 +8186,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8201,7 +8213,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8240,7 +8252,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8250,7 +8262,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8283,32 +8295,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8316,7 +8332,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8340,33 +8356,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8394,32 +8414,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8427,7 +8451,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8451,37 +8475,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8566,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8581,7 +8605,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8596,7 +8620,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8657,7 +8681,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8696,7 +8720,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8711,7 +8735,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8739,32 +8763,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8772,7 +8800,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8796,37 +8824,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8887,7 +8915,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8941,7 +8969,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9030,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9117,7 +9145,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9232,7 +9260,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9347,7 +9375,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9462,7 +9490,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9520,6 +9548,926 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>93.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,22 +1406,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2343,17 +2343,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2576,14 +2576,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>93.0</t>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3381,17 +3381,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3969,17 +3969,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5409,17 +5409,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5761,14 +5761,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>93.0</t>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6595,17 +6595,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6943,14 +6943,14 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
           <t>93.0</t>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7261,7 +7261,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7300,22 +7300,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7900,17 +7900,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8014,17 +8014,17 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8785,12 +8785,12 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8882,32 +8882,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8915,7 +8919,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8939,37 +8943,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9030,7 +9034,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9069,7 +9073,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9145,7 +9149,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9184,7 +9188,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9227,32 +9231,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9260,7 +9268,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9284,17 +9292,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9304,12 +9312,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9342,32 +9350,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9375,7 +9387,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9399,17 +9411,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9419,17 +9431,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9502,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9529,7 +9541,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9544,7 +9556,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9572,32 +9584,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9605,7 +9621,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9629,32 +9645,32 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9720,7 +9736,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9759,7 +9775,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9835,7 +9851,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9950,7 +9966,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9989,7 +10005,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10065,7 +10081,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10119,7 +10135,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10196,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10295,7 +10311,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10349,7 +10365,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10426,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10464,7 +10480,927 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>91.2</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>98.3</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2457,17 +2457,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2700,17 +2700,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4207,17 +4207,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4440,17 +4440,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5528,17 +5528,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6714,17 +6714,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7261,7 +7261,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8138,17 +8138,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8257,17 +8257,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8376,17 +8376,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8490,17 +8490,17 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8800,7 +8800,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9594,12 +9594,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9703,32 +9703,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:53</t>
@@ -9736,7 +9740,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9760,17 +9764,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9780,17 +9784,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9818,32 +9822,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9851,7 +9859,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9875,17 +9883,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9895,17 +9903,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9933,32 +9941,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9966,7 +9978,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9990,17 +10002,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10010,17 +10022,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10048,32 +10060,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10081,7 +10097,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10105,32 +10121,32 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10196,7 +10212,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10250,7 +10266,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10327,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10365,7 +10381,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10442,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10465,7 +10481,7 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10480,7 +10496,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10541,7 +10557,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10595,7 +10611,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10672,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10771,7 +10787,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10810,7 +10826,7 @@
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA88" s="2" t="inlineStr">
@@ -10886,7 +10902,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10958,7 +10974,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -11001,7 +11017,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11015,7 +11031,7 @@
       <c r="T90" s="2" t="inlineStr"/>
       <c r="U90" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="V90" s="2" t="inlineStr">
@@ -11055,7 +11071,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11132,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11160,17 +11176,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11231,7 +11247,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11280,7 +11296,7 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11346,7 +11362,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11390,17 +11406,477 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB93" s="2" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
-      <c r="AC93" s="2" t="inlineStr">
-        <is>
-          <t>16/18</t>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>91.2</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC97"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1411,17 +1411,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1645,17 +1645,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2700,17 +2700,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3381,22 +3381,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3620,17 +3620,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4933,17 +4933,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7305,17 +7305,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7781,12 +7781,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8014,22 +8014,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8138,17 +8138,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8376,17 +8376,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8725,17 +8725,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8800,7 +8800,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8963,17 +8963,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9660,22 +9660,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9784,17 +9784,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9913,7 +9913,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10022,17 +10022,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10409,32 +10409,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10442,7 +10446,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10466,17 +10470,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10486,17 +10490,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10524,32 +10528,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10557,7 +10565,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10581,17 +10589,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10601,17 +10609,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10672,7 +10680,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10754,32 +10762,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10787,7 +10799,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10811,17 +10823,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10831,12 +10843,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10869,32 +10881,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -10902,7 +10918,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10926,17 +10942,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -10946,12 +10962,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -10984,32 +11000,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:53</t>
@@ -11017,7 +11037,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11041,17 +11061,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11061,12 +11081,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11099,32 +11119,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:53</t>
@@ -11132,7 +11156,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11156,17 +11180,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11176,17 +11200,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11214,32 +11238,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -11247,7 +11275,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11271,37 +11299,37 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11329,32 +11357,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11362,7 +11394,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11386,17 +11418,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11406,17 +11438,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11477,7 +11509,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11516,7 +11548,7 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11592,7 +11624,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11636,17 +11668,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11707,7 +11739,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11746,7 +11778,7 @@
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
@@ -11761,7 +11793,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11822,7 +11854,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11866,17 +11898,362 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>91.8</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB97" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
-      <c r="AC97" s="2" t="inlineStr">
-        <is>
-          <t>14/18</t>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>91.2</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1645,17 +1645,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1760,17 +1760,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3620,17 +3620,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3735,17 +3735,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4933,17 +4933,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6242,17 +6242,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7543,17 +7543,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7672,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8725,17 +8725,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10490,17 +10490,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10799,7 +10799,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11394,7 +11394,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11476,32 +11476,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11509,7 +11513,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11533,17 +11537,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11553,17 +11557,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11591,32 +11595,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11624,7 +11632,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11648,17 +11656,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11668,17 +11676,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11747,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11793,7 +11801,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11854,7 +11862,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11908,7 +11916,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11969,7 +11977,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12084,7 +12092,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12128,17 +12136,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -12199,7 +12207,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12253,7 +12261,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-浦东78路.xlsx
+++ b/data/export/2026-10-26-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2581,17 +2581,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5766,17 +5766,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6948,17 +6948,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7548,12 +7548,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9665,12 +9665,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10495,12 +10495,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10799,7 +10799,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10843,17 +10843,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11319,12 +11319,12 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11486,24 +11486,24 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11562,12 +11562,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11605,12 +11605,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11681,12 +11681,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11747,7 +11747,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11829,32 +11829,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:37</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11862,7 +11866,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11886,17 +11890,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11906,17 +11910,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11944,32 +11948,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -11977,7 +11985,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12001,17 +12009,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12021,12 +12029,12 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12092,7 +12100,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12141,12 +12149,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -12207,7 +12215,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12261,7 +12269,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
